--- a/exports/FORTIS_full_report.xlsx
+++ b/exports/FORTIS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:U54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.13</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>276.5</v>
+        <v>269.35</v>
       </c>
       <c r="I2" t="n">
         <v>275.37265878</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.33</v>
+        <v>-6.8</v>
       </c>
       <c r="L2" t="n">
-        <v>5.19</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>1.19</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
         <v>0.99</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.11</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44622.55208333334</v>
+        <v>44623.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>246.7</v>
+        <v>262.25</v>
       </c>
       <c r="I3" t="n">
         <v>253.7672769394263</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K3" t="n">
-        <v>8.41</v>
+        <v>2.64</v>
       </c>
       <c r="L3" t="n">
         <v>3.88</v>
@@ -612,7 +647,7 @@
         <v>1.62</v>
       </c>
       <c r="N3" t="n">
-        <v>3.53</v>
+        <v>7.22</v>
       </c>
       <c r="O3" t="n">
         <v>-4.9</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.83</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>262.75</v>
+        <v>258.2</v>
       </c>
       <c r="I4" t="n">
         <v>262.0050024844378</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>0.19</v>
+        <v>-1.54</v>
       </c>
       <c r="L4" t="n">
         <v>5.87</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.27</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44746.55208333334</v>
+        <v>44747.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>241</v>
+        <v>242.7</v>
       </c>
       <c r="I5" t="n">
         <v>241.4520196960684</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>61</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>6.66</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>2.05</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.39</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44825.55208333334</v>
+        <v>44826.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>312</v>
+        <v>258.35</v>
       </c>
       <c r="I6" t="n">
         <v>292.680220504373</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>78.16666666666667</v>
+        <v>79</v>
       </c>
       <c r="K6" t="n">
-        <v>28.55</v>
+        <v>6.45</v>
       </c>
       <c r="L6" t="n">
         <v>3.05</v>
@@ -783,7 +854,7 @@
         <v>1.71</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>15.13</v>
       </c>
       <c r="O6" t="n">
         <v>-0.5</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>28.55</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44867.38541666666</v>
+        <v>44867.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>280</v>
+        <v>281.05</v>
       </c>
       <c r="I7" t="n">
         <v>280.56452022152</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.380000000000001</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>24.99</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.67</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44888.38541666666</v>
+        <v>44888.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>281</v>
+        <v>276.9</v>
       </c>
       <c r="I8" t="n">
         <v>278.9182906071595</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02</v>
+        <v>-1.48</v>
       </c>
       <c r="L8" t="n">
         <v>2.15</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.77</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>261.35</v>
+        <v>263.7</v>
       </c>
       <c r="I9" t="n">
         <v>263.3171430865191</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>126</v>
+        <v>127.8333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>5.62</v>
+        <v>4.77</v>
       </c>
       <c r="L9" t="n">
         <v>6.83</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>175</v>
+        <v>176</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.38</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45076.55208333334</v>
+        <v>45077.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>279.75</v>
+        <v>275.15</v>
       </c>
       <c r="I10" t="n">
         <v>276.0169213615335</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K10" t="n">
-        <v>6.09</v>
+        <v>4.34</v>
       </c>
       <c r="L10" t="n">
         <v>4.74</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.09</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45089.55208333334</v>
+        <v>45090.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>283</v>
+        <v>288.55</v>
       </c>
       <c r="I11" t="n">
         <v>287.7189446677867</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.85</v>
+        <v>-4.87</v>
       </c>
       <c r="L11" t="n">
-        <v>3.73</v>
+        <v>5.29</v>
       </c>
       <c r="M11" t="n">
         <v>0.97</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.8</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45145.38541666666</v>
+        <v>45145.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>328</v>
+        <v>322.5</v>
       </c>
       <c r="I12" t="n">
         <v>326.6725266040419</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>55</v>
+        <v>55.16666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>13.67</v>
+        <v>11.77</v>
       </c>
       <c r="L12" t="n">
         <v>2.62</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45166.38541666666</v>
+        <v>45166.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>330.5</v>
+        <v>335</v>
       </c>
       <c r="I13" t="n">
         <v>334.3832801437226</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.48</v>
+        <v>-3.88</v>
       </c>
       <c r="L13" t="n">
         <v>4.79</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45187.38541666666</v>
+        <v>45187.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>329.8</v>
+        <v>326.1</v>
       </c>
       <c r="I14" t="n">
         <v>327.9250119625806</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.55</v>
+        <v>-2.66</v>
       </c>
       <c r="L14" t="n">
         <v>3.99</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>5.15</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45196.55208333334</v>
+        <v>45197.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>342.1</v>
+        <v>344.15</v>
       </c>
       <c r="I15" t="n">
         <v>342.9063656286785</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.91</v>
+        <v>-5.54</v>
       </c>
       <c r="L15" t="n">
-        <v>4.91</v>
+        <v>6.82</v>
       </c>
       <c r="M15" t="n">
         <v>1.2</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45205.38541666666</v>
+        <v>45205.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>329.9</v>
+        <v>327.5</v>
       </c>
       <c r="I16" t="n">
         <v>328.5891610185474</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.14</v>
+        <v>-4.84</v>
       </c>
       <c r="L16" t="n">
-        <v>4.94</v>
+        <v>5.16</v>
       </c>
       <c r="M16" t="n">
         <v>0.1</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.4</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45238.38541666666</v>
+        <v>45238.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>338.3</v>
+        <v>340.2</v>
       </c>
       <c r="I17" t="n">
         <v>338.4074605192959</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.3</v>
+        <v>-3.88</v>
       </c>
       <c r="L17" t="n">
-        <v>3.74</v>
+        <v>4.26</v>
       </c>
       <c r="M17" t="n">
         <v>1.37</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.75</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45335.55208333334</v>
+        <v>45336.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>434.5</v>
+        <v>426</v>
       </c>
       <c r="I18" t="n">
         <v>426.6158048722721</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>97</v>
+        <v>97.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>27.72</v>
+        <v>25.22</v>
       </c>
       <c r="L18" t="n">
         <v>0.72</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.9</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45362.38541666666</v>
+        <v>45362.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>408.85</v>
+        <v>411.6</v>
       </c>
       <c r="I19" t="n">
         <v>409.6822278668531</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>4.03</v>
+        <v>3.38</v>
       </c>
       <c r="L19" t="n">
         <v>6.31</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>459.35</v>
+        <v>436.25</v>
       </c>
       <c r="I20" t="n">
         <v>442.3450637150974</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>84</v>
+        <v>84.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>11.6</v>
+        <v>5.99</v>
       </c>
       <c r="L20" t="n">
         <v>8.16</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.23</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45456.38541666666</v>
+        <v>45456.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>469.45</v>
+        <v>489</v>
       </c>
       <c r="I21" t="n">
         <v>481.2088471739217</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.61</v>
+        <v>-12.09</v>
       </c>
       <c r="L21" t="n">
-        <v>10.01</v>
+        <v>12.09</v>
       </c>
       <c r="M21" t="n">
         <v>2.16</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.51</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45474.55208333334</v>
+        <v>45475.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>471.25</v>
+        <v>460.8</v>
       </c>
       <c r="I22" t="n">
         <v>464.6980223713177</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.63</v>
+        <v>-5.77</v>
       </c>
       <c r="L22" t="n">
-        <v>4.08</v>
+        <v>5.83</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>4.21</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.19</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45488.55208333334</v>
+        <v>45489.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>486.2</v>
+        <v>489.65</v>
       </c>
       <c r="I23" t="n">
         <v>487.3108876427963</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.51</v>
+        <v>-6.26</v>
       </c>
       <c r="L23" t="n">
-        <v>6.51</v>
+        <v>6.77</v>
       </c>
       <c r="M23" t="n">
         <v>1.29</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.84</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45622.55208333334</v>
+        <v>45623.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>664</v>
+        <v>654.5</v>
       </c>
       <c r="I24" t="n">
         <v>656.0829938348076</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>133.1666666666667</v>
+        <v>134</v>
       </c>
       <c r="K24" t="n">
-        <v>35.61</v>
+        <v>33.67</v>
       </c>
       <c r="L24" t="n">
         <v>2.99</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>11.08</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45629.55208333334</v>
+        <v>45630.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="I25" t="n">
         <v>709.3640554704846</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.26</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>7.85</v>
+        <v>9.18</v>
       </c>
       <c r="M25" t="n">
         <v>0.72</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>687.75</v>
+        <v>674.1</v>
       </c>
       <c r="I26" t="n">
         <v>678.651869327985</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.41</v>
+        <v>-5.32</v>
       </c>
       <c r="L26" t="n">
-        <v>3.79</v>
+        <v>5.67</v>
       </c>
       <c r="M26" t="n">
         <v>0.06</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.37</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45653.55208333334</v>
+        <v>45656.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>679.9</v>
+        <v>707.4</v>
       </c>
       <c r="I27" t="n">
         <v>705.1029365442424</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.86</v>
+        <v>-4.94</v>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>5.1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>3.36</v>
       </c>
       <c r="O27" t="n">
         <v>-1.16</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,25 +2351,25 @@
         <v>7.94</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45667.55208333334</v>
+        <v>45670.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>685.95</v>
+        <v>662.05</v>
       </c>
       <c r="I28" t="n">
         <v>684.899965964288</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.03</v>
+        <v>-6.41</v>
       </c>
       <c r="L28" t="n">
-        <v>3.58</v>
+        <v>6.73</v>
       </c>
       <c r="M28" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="N28" t="n">
         <v>3.66</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.49</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45686.38541666666</v>
+        <v>45686.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>622.2</v>
+        <v>629</v>
       </c>
       <c r="I29" t="n">
         <v>626.2338060611609</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>6.02</v>
+        <v>4.99</v>
       </c>
       <c r="L29" t="n">
         <v>3.76</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45699.38541666666</v>
+        <v>45699.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>615.2</v>
+        <v>613.1</v>
       </c>
       <c r="I30" t="n">
         <v>614.0701896180366</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.19</v>
+        <v>-2.53</v>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>3.09</v>
       </c>
       <c r="M30" t="n">
         <v>0.49</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.15</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45719.55208333334</v>
+        <v>45720.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>625</v>
+        <v>644</v>
       </c>
       <c r="I31" t="n">
         <v>642.9729656986146</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.94</v>
+        <v>-5.04</v>
       </c>
       <c r="L31" t="n">
-        <v>3.64</v>
+        <v>7</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>9.27</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45728.55208333334</v>
+        <v>45729.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>614.95</v>
+        <v>605.95</v>
       </c>
       <c r="I32" t="n">
         <v>606.2422229741562</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.51</v>
+        <v>-5.91</v>
       </c>
       <c r="L32" t="n">
-        <v>5.09</v>
+        <v>6.89</v>
       </c>
       <c r="M32" t="n">
         <v>0.93</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45737.55208333334</v>
+        <v>45740.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>629.6</v>
+        <v>647.7</v>
       </c>
       <c r="I33" t="n">
         <v>639.6167213165385</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.9</v>
+        <v>-6.89</v>
       </c>
       <c r="L33" t="n">
-        <v>6.35</v>
+        <v>7.26</v>
       </c>
       <c r="M33" t="n">
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>3.72</v>
       </c>
       <c r="O33" t="n">
         <v>-1.5</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>648.85</v>
+        <v>627</v>
       </c>
       <c r="I34" t="n">
         <v>638.4282104251922</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K34" t="n">
-        <v>0.18</v>
+        <v>-3.2</v>
       </c>
       <c r="L34" t="n">
-        <v>2.63</v>
+        <v>8.01</v>
       </c>
       <c r="M34" t="n">
-        <v>2.89</v>
+        <v>6.6</v>
       </c>
       <c r="N34" t="n">
         <v>3.4</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.1</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45776.55208333334</v>
+        <v>45777.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>666</v>
+        <v>697.85</v>
       </c>
       <c r="I35" t="n">
         <v>684.0528515560829</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.22</v>
+        <v>-11.3</v>
       </c>
       <c r="L35" t="n">
         <v>11.59</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.28</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>771.55</v>
+        <v>760</v>
       </c>
       <c r="I36" t="n">
         <v>769.5569095697606</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>72</v>
       </c>
       <c r="K36" t="n">
-        <v>10.56</v>
+        <v>8.91</v>
       </c>
       <c r="L36" t="n">
         <v>7.33</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>6.54</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45853.55208333334</v>
+        <v>45854.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>799</v>
+        <v>802.2</v>
       </c>
       <c r="I37" t="n">
         <v>802.0835498435266</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.13</v>
+        <v>-5.55</v>
       </c>
       <c r="L37" t="n">
-        <v>6.24</v>
+        <v>6.43</v>
       </c>
       <c r="M37" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="N37" t="n">
         <v>3.22</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>5.07</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45894.38541666666</v>
+        <v>45894.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>920.55</v>
+        <v>915.75</v>
       </c>
       <c r="I38" t="n">
         <v>919.6524483003171</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>14.75</v>
+        <v>14.15</v>
       </c>
       <c r="L38" t="n">
         <v>1.43</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>4.57</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45903.38541666666</v>
+        <v>45903.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>939.95</v>
+        <v>959</v>
       </c>
       <c r="I39" t="n">
         <v>948.5116132005363</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.64</v>
+        <v>-4.72</v>
       </c>
       <c r="L39" t="n">
-        <v>3.68</v>
+        <v>4.72</v>
       </c>
       <c r="M39" t="n">
         <v>0.8</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>5.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>944.6</v>
+        <v>934.1</v>
       </c>
       <c r="I40" t="n">
         <v>940.4869944623947</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.5</v>
+        <v>-2.6</v>
       </c>
       <c r="L40" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="M40" t="n">
-        <v>0.37</v>
+        <v>0.59</v>
       </c>
       <c r="N40" t="n">
         <v>1.5</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>4.55</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45930.55208333334</v>
+        <v>45931.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>969.8</v>
+        <v>986.45</v>
       </c>
       <c r="I41" t="n">
         <v>971.5390918970153</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.82</v>
+        <v>-5.6</v>
       </c>
       <c r="L41" t="n">
-        <v>4.37</v>
+        <v>6.47</v>
       </c>
       <c r="M41" t="n">
         <v>0.48</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.28</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45953.38541666666</v>
+        <v>45953.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>1058.35</v>
+        <v>1047.4</v>
       </c>
       <c r="I42" t="n">
         <v>1052.468379965339</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>7.29</v>
+        <v>6.18</v>
       </c>
       <c r="L42" t="n">
         <v>1.92</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.89</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>889</v>
+        <v>905.8</v>
       </c>
       <c r="I43" t="n">
         <v>896.3925755607049</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>57</v>
+        <v>59.83333333333334</v>
       </c>
       <c r="K43" t="n">
-        <v>15.12</v>
+        <v>13.52</v>
       </c>
       <c r="L43" t="n">
         <v>1.94</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>5.11</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>902.4</v>
+        <v>890.25</v>
       </c>
       <c r="I44" t="n">
         <v>899.7205824298896</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.38</v>
+        <v>-1.72</v>
       </c>
       <c r="L44" t="n">
         <v>3.37</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.51</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>853.9</v>
+        <v>890.45</v>
       </c>
       <c r="I45" t="n">
         <v>878.790188478172</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K45" t="n">
-        <v>4.08</v>
+        <v>-0.02</v>
       </c>
       <c r="L45" t="n">
         <v>3.01</v>
@@ -3006,7 +3545,7 @@
         <v>1.79</v>
       </c>
       <c r="N45" t="n">
-        <v>2.96</v>
+        <v>4.46</v>
       </c>
       <c r="O45" t="n">
         <v>-1.05</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>928.6</v>
+        <v>911.6</v>
       </c>
       <c r="I46" t="n">
         <v>913.272663875824</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>4.28</v>
+        <v>2.38</v>
       </c>
       <c r="L46" t="n">
         <v>4.18</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.39</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46119.38541666666</v>
+        <v>46119.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>829.65</v>
+        <v>839.8</v>
       </c>
       <c r="I47" t="n">
         <v>837.790886888788</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K47" t="n">
-        <v>8.99</v>
+        <v>7.88</v>
       </c>
       <c r="L47" t="n">
         <v>1.78</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.93</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46174.38541666666</v>
+        <v>46174.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>929.75</v>
+        <v>928.85</v>
       </c>
       <c r="I48" t="n">
         <v>928.9144653159768</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>54.83333333333334</v>
+        <v>55</v>
       </c>
       <c r="K48" t="n">
-        <v>10.71</v>
+        <v>10.6</v>
       </c>
       <c r="L48" t="n">
         <v>1.59</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.37</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>966</v>
+        <v>1002.7</v>
       </c>
       <c r="I49" t="n">
         <v>966.9021722718572</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-4</v>
+        <v>-7.95</v>
       </c>
       <c r="L49" t="n">
-        <v>4.65</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M49" t="n">
         <v>0.45</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46230.55208333334</v>
+        <v>46231.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>943</v>
+        <v>937.8</v>
       </c>
       <c r="I50" t="n">
         <v>940.9196092537512</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.95</v>
+        <v>-6.47</v>
       </c>
       <c r="L50" t="n">
         <v>7.48</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.29</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46241.38541666666</v>
+        <v>46241.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>928.9</v>
+        <v>959.8</v>
       </c>
       <c r="I51" t="n">
         <v>958.8709205564862</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>0.95</v>
+        <v>-2.35</v>
       </c>
       <c r="L51" t="n">
         <v>4.46</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.04</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>933.9</v>
+        <v>884.85</v>
       </c>
       <c r="I52" t="n">
         <v>904.2423239143217</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.7</v>
+        <v>-7.81</v>
       </c>
       <c r="L52" t="n">
-        <v>3.77</v>
+        <v>8.25</v>
       </c>
       <c r="M52" t="n">
         <v>0.38</v>
       </c>
       <c r="N52" t="n">
-        <v>1.55</v>
+        <v>5.13</v>
       </c>
       <c r="O52" t="n">
         <v>4.55</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.1</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46322.55208333334</v>
+        <v>46323.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>737</v>
+        <v>756.05</v>
       </c>
       <c r="I53" t="n">
         <v>750.9778621073692</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K53" t="n">
-        <v>16.71</v>
+        <v>14.56</v>
       </c>
       <c r="L53" t="n">
         <v>6.45</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3522,6 +4169,12 @@
       <c r="Q54" t="n">
         <v>2</v>
       </c>
+      <c r="R54" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5624,7 +6277,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="6">
@@ -5634,7 +6287,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -5644,7 +6297,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>133.2</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
@@ -5654,7 +6307,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -5664,7 +6317,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="10">
@@ -5674,7 +6327,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75.7</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="11">
@@ -5714,7 +6367,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.69</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="15">
@@ -5724,7 +6377,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.15</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="16">
@@ -5734,7 +6387,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.22</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="17">
@@ -5744,7 +6397,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35.61</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="18">
@@ -5754,7 +6407,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="19">
@@ -5764,7 +6417,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.81</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="20">
@@ -5774,7 +6427,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.94</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="21">
@@ -5794,7 +6447,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -5814,7 +6467,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25">
@@ -5824,7 +6477,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.84</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="26">
@@ -5834,7 +6487,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.35</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="27">
@@ -5844,7 +6497,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.130000000000001</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="28">
@@ -5854,7 +6507,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
